--- a/backend/upload/sp_2022_kyokwa_subject.xlsx
+++ b/backend/upload/sp_2022_kyokwa_subject.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\github\StudyPlanner\backend\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F344100-65E0-4FD1-BA4F-3E44E6C133BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303701FA-7A05-4C66-873C-E4C9FB777BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30930" yWindow="2235" windowWidth="21600" windowHeight="11295" xr2:uid="{BFE6C9BE-DCA1-4C8F-8EA1-C526A2486435}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BFE6C9BE-DCA1-4C8F-8EA1-C526A2486435}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="341">
   <si>
     <t>ID</t>
   </si>
@@ -59,982 +59,1013 @@
     <t>과목코드</t>
   </si>
   <si>
-    <t>H250111</t>
-  </si>
-  <si>
     <t>국어</t>
   </si>
   <si>
-    <t>01</t>
-  </si>
-  <si>
     <t>공통과목</t>
   </si>
   <si>
     <t>공통국어1</t>
   </si>
   <si>
-    <t>H250112</t>
-  </si>
-  <si>
     <t>공통국어2</t>
   </si>
   <si>
-    <t>H250121</t>
-  </si>
-  <si>
     <t>일반선택</t>
   </si>
   <si>
     <t>독서와 작문</t>
   </si>
   <si>
-    <t>H250122</t>
-  </si>
-  <si>
     <t>문학</t>
   </si>
   <si>
-    <t>H250123</t>
-  </si>
-  <si>
     <t>화법과 언어</t>
   </si>
   <si>
-    <t>H250131</t>
-  </si>
-  <si>
     <t>진로선택</t>
   </si>
   <si>
     <t>문학과 영상</t>
   </si>
   <si>
-    <t>H250132</t>
-  </si>
-  <si>
     <t>주제 탐구 독서</t>
   </si>
   <si>
-    <t>H250133</t>
-  </si>
-  <si>
     <t>직무 의사소통</t>
   </si>
   <si>
-    <t>H250141</t>
-  </si>
-  <si>
     <t>융합선택</t>
   </si>
   <si>
     <t>독서 토론과 글쓰기</t>
   </si>
   <si>
-    <t>H250142</t>
-  </si>
-  <si>
     <t>매체 의사소통</t>
   </si>
   <si>
-    <t>H250143</t>
-  </si>
-  <si>
     <t>언어생활 탐구</t>
   </si>
   <si>
-    <t>H250211</t>
-  </si>
-  <si>
     <t>수학</t>
   </si>
   <si>
-    <t>02</t>
-  </si>
-  <si>
     <t>공통수학1</t>
   </si>
   <si>
-    <t>H250212</t>
-  </si>
-  <si>
     <t>공통수학2</t>
   </si>
   <si>
-    <t>H250213</t>
-  </si>
-  <si>
     <t>기본수학1</t>
   </si>
   <si>
-    <t>H250214</t>
-  </si>
-  <si>
     <t>기본수학2</t>
   </si>
   <si>
-    <t>H250221</t>
-  </si>
-  <si>
     <t>대수</t>
   </si>
   <si>
-    <t>H250222</t>
-  </si>
-  <si>
     <t>미적분I</t>
   </si>
   <si>
-    <t>H250223</t>
-  </si>
-  <si>
     <t>확률과 통계</t>
   </si>
   <si>
-    <t>H250231</t>
-  </si>
-  <si>
     <t>경제 수학</t>
   </si>
   <si>
-    <t>H250232</t>
-  </si>
-  <si>
     <t>기하</t>
   </si>
   <si>
-    <t>H250233</t>
-  </si>
-  <si>
     <t>미적분II</t>
   </si>
   <si>
-    <t>H250234</t>
-  </si>
-  <si>
     <t>인공지능 수학</t>
   </si>
   <si>
-    <t>H250235</t>
-  </si>
-  <si>
     <t>직무 수학</t>
   </si>
   <si>
-    <t>H250241</t>
-  </si>
-  <si>
     <t>수학과 문화</t>
   </si>
   <si>
-    <t>H250242</t>
-  </si>
-  <si>
     <t>수학과제 탐구</t>
   </si>
   <si>
-    <t>H250243</t>
-  </si>
-  <si>
     <t>실용 통계</t>
   </si>
   <si>
-    <t>H250311</t>
-  </si>
-  <si>
     <t>영어</t>
   </si>
   <si>
-    <t>03</t>
-  </si>
-  <si>
     <t>공통영어1</t>
   </si>
   <si>
-    <t>H250312</t>
-  </si>
-  <si>
     <t>공통영어2</t>
   </si>
   <si>
-    <t>H250313</t>
-  </si>
-  <si>
     <t>기본영어1 기본영어2</t>
   </si>
   <si>
-    <t>H250321</t>
-  </si>
-  <si>
     <t>영어 독해와 작문</t>
   </si>
   <si>
-    <t>H250322</t>
-  </si>
-  <si>
     <t>영어I</t>
   </si>
   <si>
-    <t>H250323</t>
-  </si>
-  <si>
     <t>영어II</t>
   </si>
   <si>
-    <t>H250331</t>
-  </si>
-  <si>
     <t>심화 영어</t>
   </si>
   <si>
-    <t>H250332</t>
-  </si>
-  <si>
     <t>심화 영어 독해와 작문</t>
   </si>
   <si>
-    <t>H250333</t>
-  </si>
-  <si>
     <t>영미 문학 읽기</t>
   </si>
   <si>
-    <t>H250334</t>
-  </si>
-  <si>
     <t>영어 발표와 토론</t>
   </si>
   <si>
-    <t>H250335</t>
-  </si>
-  <si>
     <t>직무 영어</t>
   </si>
   <si>
-    <t>H250341</t>
-  </si>
-  <si>
     <t>미디어 영어</t>
   </si>
   <si>
-    <t>H250342</t>
-  </si>
-  <si>
     <t>세계 문화와 영어</t>
   </si>
   <si>
-    <t>H250343</t>
-  </si>
-  <si>
     <t>실생활 영어 회화</t>
   </si>
   <si>
-    <t>H250411</t>
-  </si>
-  <si>
     <t>사회(역사/도덕 포함)</t>
   </si>
   <si>
-    <t>04</t>
-  </si>
-  <si>
     <t>통합사회1</t>
   </si>
   <si>
-    <t>H250412</t>
-  </si>
-  <si>
     <t>통합사회2</t>
   </si>
   <si>
-    <t>H250413</t>
-  </si>
-  <si>
     <t>한국사1</t>
   </si>
   <si>
-    <t>H250414</t>
-  </si>
-  <si>
     <t>한국사2</t>
   </si>
   <si>
-    <t>H250421</t>
-  </si>
-  <si>
     <t>사회와 문화</t>
   </si>
   <si>
-    <t>H250422</t>
-  </si>
-  <si>
     <t>세계사</t>
   </si>
   <si>
-    <t>H250423</t>
-  </si>
-  <si>
     <t>세계시민과 지리</t>
   </si>
   <si>
-    <t>H250424</t>
-  </si>
-  <si>
     <t>현대사회와 윤리</t>
   </si>
   <si>
-    <t>H250431</t>
-  </si>
-  <si>
     <t>경제</t>
   </si>
   <si>
-    <t>H250432</t>
-  </si>
-  <si>
     <t>국제 관계의 이해</t>
   </si>
   <si>
-    <t>H250433</t>
-  </si>
-  <si>
     <t>도시의 미래 탐구</t>
   </si>
   <si>
-    <t>H250434</t>
-  </si>
-  <si>
     <t>동아시아 역사 기행</t>
   </si>
   <si>
-    <t>H250435</t>
-  </si>
-  <si>
     <t>법과 사회</t>
   </si>
   <si>
-    <t>H250436</t>
-  </si>
-  <si>
     <t>윤리와 사상</t>
   </si>
   <si>
-    <t>H250437</t>
-  </si>
-  <si>
     <t>인문학과 윤리</t>
   </si>
   <si>
-    <t>H250438</t>
-  </si>
-  <si>
     <t>정치</t>
   </si>
   <si>
-    <t>H250439</t>
-  </si>
-  <si>
     <t>한국지리 탐구</t>
   </si>
   <si>
-    <t>H250441</t>
-  </si>
-  <si>
     <t>금융과 경제생활</t>
   </si>
   <si>
-    <t>H250442</t>
-  </si>
-  <si>
     <t>기후변화와 지속가능한 세계</t>
   </si>
   <si>
-    <t>H250443</t>
-  </si>
-  <si>
     <t>사회문제 탐구</t>
   </si>
   <si>
-    <t>H250444</t>
-  </si>
-  <si>
     <t>여행지리</t>
   </si>
   <si>
-    <t>H250445</t>
-  </si>
-  <si>
     <t>역사로 탐구하는 현대 세계</t>
   </si>
   <si>
-    <t>H250446</t>
-  </si>
-  <si>
     <t>윤리문제 탐구</t>
   </si>
   <si>
-    <t>H250511</t>
-  </si>
-  <si>
     <t>과학</t>
   </si>
   <si>
-    <t>05</t>
-  </si>
-  <si>
     <t>과학탐구실험1</t>
   </si>
   <si>
-    <t>H250512</t>
-  </si>
-  <si>
     <t>과학탐구실험2</t>
   </si>
   <si>
-    <t>H250513</t>
-  </si>
-  <si>
     <t>통합과학1</t>
   </si>
   <si>
-    <t>H250514</t>
-  </si>
-  <si>
     <t>통합과학2</t>
   </si>
   <si>
-    <t>H250521</t>
-  </si>
-  <si>
     <t>물리학</t>
   </si>
   <si>
-    <t>H250522</t>
-  </si>
-  <si>
     <t>생명과학</t>
   </si>
   <si>
-    <t>H250523</t>
-  </si>
-  <si>
     <t>지구과학</t>
   </si>
   <si>
-    <t>H250524</t>
-  </si>
-  <si>
     <t>화학</t>
   </si>
   <si>
-    <t>H250531</t>
-  </si>
-  <si>
     <t>물질과 에너지</t>
   </si>
   <si>
-    <t>H250532</t>
-  </si>
-  <si>
     <t>생물의 유전</t>
   </si>
   <si>
-    <t>H250533</t>
-  </si>
-  <si>
     <t>세포와 물질대사</t>
   </si>
   <si>
-    <t>H250534</t>
-  </si>
-  <si>
     <t>역학과 에너지</t>
   </si>
   <si>
-    <t>H250535</t>
-  </si>
-  <si>
     <t>전자기와 양자</t>
   </si>
   <si>
-    <t>H250536</t>
-  </si>
-  <si>
     <t>지구시스템과학</t>
   </si>
   <si>
-    <t>H250537</t>
-  </si>
-  <si>
     <t>행성우주과학</t>
   </si>
   <si>
-    <t>H250538</t>
-  </si>
-  <si>
     <t>화학 반응의 세계</t>
   </si>
   <si>
-    <t>H250541</t>
-  </si>
-  <si>
     <t>과학의 역사와 문화</t>
   </si>
   <si>
-    <t>H250542</t>
-  </si>
-  <si>
     <t>기후변화와 환경생태</t>
   </si>
   <si>
-    <t>H250543</t>
-  </si>
-  <si>
     <t>융합과학 탐구</t>
   </si>
   <si>
-    <t>H250621</t>
-  </si>
-  <si>
     <t>기술·가정/정보/제2외국어/한문/교양</t>
   </si>
   <si>
-    <t>06</t>
-  </si>
-  <si>
     <t>기술·가정</t>
   </si>
   <si>
-    <t>H250622</t>
-  </si>
-  <si>
     <t>독일어</t>
   </si>
   <si>
-    <t>H250623</t>
-  </si>
-  <si>
     <t>러시아어</t>
   </si>
   <si>
-    <t>H250624</t>
-  </si>
-  <si>
     <t>베트남어</t>
   </si>
   <si>
-    <t>H250625</t>
-  </si>
-  <si>
     <t>생태와 환경</t>
   </si>
   <si>
-    <t>H250626</t>
-  </si>
-  <si>
     <t>스페인어</t>
   </si>
   <si>
-    <t>H250627</t>
-  </si>
-  <si>
     <t>아랍어</t>
   </si>
   <si>
-    <t>H250628</t>
-  </si>
-  <si>
     <t>일본어</t>
   </si>
   <si>
-    <t>H250629</t>
-  </si>
-  <si>
     <t>정보</t>
   </si>
   <si>
-    <t>H2506210</t>
-  </si>
-  <si>
     <t>중국어</t>
   </si>
   <si>
-    <t>H2506211</t>
-  </si>
-  <si>
     <t>진로와 직업</t>
   </si>
   <si>
-    <t>H2506212</t>
-  </si>
-  <si>
     <t>프랑스어</t>
   </si>
   <si>
-    <t>H2506213</t>
-  </si>
-  <si>
     <t>한문</t>
   </si>
   <si>
-    <t>H250631</t>
-  </si>
-  <si>
     <t>교육의 이해</t>
   </si>
   <si>
-    <t>H250632</t>
-  </si>
-  <si>
     <t>논리와 사고</t>
   </si>
   <si>
-    <t>H250633</t>
-  </si>
-  <si>
     <t>데이터 과학</t>
   </si>
   <si>
-    <t>H250634</t>
-  </si>
-  <si>
     <t>독일어 회화</t>
   </si>
   <si>
-    <t>H250635</t>
-  </si>
-  <si>
     <t>러시아어 회화</t>
   </si>
   <si>
-    <t>H250636</t>
-  </si>
-  <si>
     <t>로봇과 공학세계</t>
   </si>
   <si>
-    <t>H250637</t>
-  </si>
-  <si>
     <t>베트남어 회화</t>
   </si>
   <si>
-    <t>H250638</t>
-  </si>
-  <si>
     <t>보건</t>
   </si>
   <si>
-    <t>H250639</t>
-  </si>
-  <si>
     <t>삶과 종교</t>
   </si>
   <si>
-    <t>H2506310</t>
-  </si>
-  <si>
     <t>생활과학 탐구</t>
   </si>
   <si>
-    <t>H2506311</t>
-  </si>
-  <si>
     <t>스페인어 회화</t>
   </si>
   <si>
-    <t>H2506312</t>
-  </si>
-  <si>
     <t>심화 독일어</t>
   </si>
   <si>
-    <t>H2506313</t>
-  </si>
-  <si>
     <t>심화 러시아어</t>
   </si>
   <si>
-    <t>H2506314</t>
-  </si>
-  <si>
     <t>심화 베트남어</t>
   </si>
   <si>
-    <t>H2506315</t>
-  </si>
-  <si>
     <t>심화 스페인어</t>
   </si>
   <si>
-    <t>H2506316</t>
-  </si>
-  <si>
     <t>심화 아랍어</t>
   </si>
   <si>
-    <t>H2506317</t>
-  </si>
-  <si>
     <t>심화 일본어</t>
   </si>
   <si>
-    <t>H2506318</t>
-  </si>
-  <si>
     <t>심화 중국어</t>
   </si>
   <si>
-    <t>H2506319</t>
-  </si>
-  <si>
     <t>심화 프랑스어</t>
   </si>
   <si>
-    <t>H2506320</t>
-  </si>
-  <si>
     <t>아랍어 회화</t>
   </si>
   <si>
-    <t>H2506321</t>
-  </si>
-  <si>
     <t>인간과 심리</t>
   </si>
   <si>
-    <t>H2506322</t>
-  </si>
-  <si>
     <t>인간과 철학</t>
   </si>
   <si>
-    <t>H2506323</t>
-  </si>
-  <si>
     <t>인공지능 기초</t>
   </si>
   <si>
-    <t>H2506324</t>
-  </si>
-  <si>
     <t>일본어 회화</t>
   </si>
   <si>
-    <t>H2506325</t>
-  </si>
-  <si>
     <t>중국어 회화</t>
   </si>
   <si>
-    <t>H2506326</t>
-  </si>
-  <si>
     <t>프랑스어 회화</t>
   </si>
   <si>
-    <t>H2506327</t>
-  </si>
-  <si>
     <t>한문 고전 읽기</t>
   </si>
   <si>
-    <t>H250641</t>
-  </si>
-  <si>
     <t>논술</t>
   </si>
   <si>
-    <t>H250642</t>
-  </si>
-  <si>
     <t>독일어권 문화</t>
   </si>
   <si>
-    <t>H250643</t>
-  </si>
-  <si>
     <t>러시아 문화</t>
   </si>
   <si>
-    <t>H250644</t>
-  </si>
-  <si>
     <t>베트남 문화</t>
   </si>
   <si>
-    <t>H250645</t>
-  </si>
-  <si>
     <t>생애 설계와 자립</t>
   </si>
   <si>
-    <t>H250646</t>
-  </si>
-  <si>
     <t>소프트웨어와 생활</t>
   </si>
   <si>
-    <t>H250647</t>
-  </si>
-  <si>
     <t>스페인어권 문화</t>
   </si>
   <si>
-    <t>H250648</t>
-  </si>
-  <si>
     <t>아동발달과 부모</t>
   </si>
   <si>
-    <t>H250649</t>
-  </si>
-  <si>
     <t>아랍 문화</t>
   </si>
   <si>
-    <t>H2506410</t>
-  </si>
-  <si>
     <t>언어생활과 한자</t>
   </si>
   <si>
-    <t>H2506411</t>
-  </si>
-  <si>
     <t>인간과 경제활동</t>
   </si>
   <si>
-    <t>H2506412</t>
-  </si>
-  <si>
     <t>일본 문화</t>
   </si>
   <si>
-    <t>H2506413</t>
-  </si>
-  <si>
     <t>중국 문화</t>
   </si>
   <si>
-    <t>H2506414</t>
-  </si>
-  <si>
     <t>지식 재산 일반</t>
   </si>
   <si>
-    <t>H2506415</t>
-  </si>
-  <si>
     <t>창의 공학 설계</t>
   </si>
   <si>
-    <t>H2506416</t>
-  </si>
-  <si>
     <t>프랑스어권 문화</t>
   </si>
   <si>
-    <t>H250821</t>
-  </si>
-  <si>
     <t>체육</t>
   </si>
   <si>
-    <t>08</t>
-  </si>
-  <si>
     <t>체육1</t>
   </si>
   <si>
-    <t>H250822</t>
-  </si>
-  <si>
     <t>체육2</t>
   </si>
   <si>
-    <t>H250831</t>
-  </si>
-  <si>
     <t>스포츠 과학</t>
   </si>
   <si>
-    <t>H250832</t>
-  </si>
-  <si>
     <t>스포츠 문화</t>
   </si>
   <si>
-    <t>H250833</t>
-  </si>
-  <si>
     <t>운동과 건강</t>
   </si>
   <si>
-    <t>H250841</t>
-  </si>
-  <si>
     <t>스포츠 생활1</t>
   </si>
   <si>
-    <t>H250921</t>
-  </si>
-  <si>
     <t>예술</t>
   </si>
   <si>
-    <t>09</t>
-  </si>
-  <si>
     <t>미술</t>
   </si>
   <si>
-    <t>H250922</t>
-  </si>
-  <si>
     <t>연극</t>
   </si>
   <si>
-    <t>H250923</t>
-  </si>
-  <si>
     <t>음악</t>
   </si>
   <si>
-    <t>H250931</t>
-  </si>
-  <si>
     <t>미술 감상과 비평</t>
   </si>
   <si>
-    <t>H250932</t>
-  </si>
-  <si>
     <t>미술 창작</t>
   </si>
   <si>
-    <t>H250933</t>
-  </si>
-  <si>
     <t>음악 감상과 비평</t>
   </si>
   <si>
-    <t>H250934</t>
-  </si>
-  <si>
     <t>음악 연주와 창작</t>
   </si>
   <si>
-    <t>H250941</t>
-  </si>
-  <si>
     <t>미술과 매체</t>
   </si>
   <si>
-    <t>H250942</t>
-  </si>
-  <si>
     <t>음악과 미디어</t>
+  </si>
+  <si>
+    <t>수능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수능국어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>표점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22H01</t>
+  </si>
+  <si>
+    <t>석차등급,성취</t>
+  </si>
+  <si>
+    <t>22H0111</t>
+  </si>
+  <si>
+    <t>22H0112</t>
+  </si>
+  <si>
+    <t>22H0121</t>
+  </si>
+  <si>
+    <t>22H0122</t>
+  </si>
+  <si>
+    <t>22H0123</t>
+  </si>
+  <si>
+    <t>22H0131</t>
+  </si>
+  <si>
+    <t>22H0132</t>
+  </si>
+  <si>
+    <t>22H0133</t>
+  </si>
+  <si>
+    <t>22H0141</t>
+  </si>
+  <si>
+    <t>22H0142</t>
+  </si>
+  <si>
+    <t>22H0143</t>
+  </si>
+  <si>
+    <t>22H0211</t>
+  </si>
+  <si>
+    <t>22H02</t>
+  </si>
+  <si>
+    <t>22H0212</t>
+  </si>
+  <si>
+    <t>22H0213</t>
+  </si>
+  <si>
+    <t>22H0214</t>
+  </si>
+  <si>
+    <t>22H0221</t>
+  </si>
+  <si>
+    <t>22H0222</t>
+  </si>
+  <si>
+    <t>22H0223</t>
+  </si>
+  <si>
+    <t>22H0231</t>
+  </si>
+  <si>
+    <t>22H0232</t>
+  </si>
+  <si>
+    <t>22H0233</t>
+  </si>
+  <si>
+    <t>22H0234</t>
+  </si>
+  <si>
+    <t>22H0235</t>
+  </si>
+  <si>
+    <t>22H0241</t>
+  </si>
+  <si>
+    <t>22H0242</t>
+  </si>
+  <si>
+    <t>22H0243</t>
+  </si>
+  <si>
+    <t>22H0311</t>
+  </si>
+  <si>
+    <t>22H03</t>
+  </si>
+  <si>
+    <t>22H0312</t>
+  </si>
+  <si>
+    <t>22H0313</t>
+  </si>
+  <si>
+    <t>22H0321</t>
+  </si>
+  <si>
+    <t>22H0322</t>
+  </si>
+  <si>
+    <t>22H0323</t>
+  </si>
+  <si>
+    <t>22H0331</t>
+  </si>
+  <si>
+    <t>22H0332</t>
+  </si>
+  <si>
+    <t>22H0333</t>
+  </si>
+  <si>
+    <t>22H0334</t>
+  </si>
+  <si>
+    <t>22H0335</t>
+  </si>
+  <si>
+    <t>22H0341</t>
+  </si>
+  <si>
+    <t>22H0342</t>
+  </si>
+  <si>
+    <t>22H0343</t>
+  </si>
+  <si>
+    <t>22H0411</t>
+  </si>
+  <si>
+    <t>22H04</t>
+  </si>
+  <si>
+    <t>22H0412</t>
+  </si>
+  <si>
+    <t>22H0413</t>
+  </si>
+  <si>
+    <t>22H0414</t>
+  </si>
+  <si>
+    <t>22H0421</t>
+  </si>
+  <si>
+    <t>22H0422</t>
+  </si>
+  <si>
+    <t>22H0423</t>
+  </si>
+  <si>
+    <t>22H0424</t>
+  </si>
+  <si>
+    <t>22H0431</t>
+  </si>
+  <si>
+    <t>22H0432</t>
+  </si>
+  <si>
+    <t>22H0433</t>
+  </si>
+  <si>
+    <t>22H0434</t>
+  </si>
+  <si>
+    <t>22H0435</t>
+  </si>
+  <si>
+    <t>22H0436</t>
+  </si>
+  <si>
+    <t>22H0437</t>
+  </si>
+  <si>
+    <t>22H0438</t>
+  </si>
+  <si>
+    <t>22H0439</t>
+  </si>
+  <si>
+    <t>22H0441</t>
+  </si>
+  <si>
+    <t>22H0442</t>
+  </si>
+  <si>
+    <t>22H0443</t>
+  </si>
+  <si>
+    <t>22H0444</t>
+  </si>
+  <si>
+    <t>22H0445</t>
+  </si>
+  <si>
+    <t>22H0446</t>
+  </si>
+  <si>
+    <t>22H0511</t>
+  </si>
+  <si>
+    <t>22H05</t>
+  </si>
+  <si>
+    <t>22H0512</t>
+  </si>
+  <si>
+    <t>22H0513</t>
+  </si>
+  <si>
+    <t>22H0514</t>
+  </si>
+  <si>
+    <t>22H0521</t>
+  </si>
+  <si>
+    <t>22H0522</t>
+  </si>
+  <si>
+    <t>22H0523</t>
+  </si>
+  <si>
+    <t>22H0524</t>
+  </si>
+  <si>
+    <t>22H0531</t>
+  </si>
+  <si>
+    <t>22H0532</t>
+  </si>
+  <si>
+    <t>22H0533</t>
+  </si>
+  <si>
+    <t>22H0534</t>
+  </si>
+  <si>
+    <t>22H0535</t>
+  </si>
+  <si>
+    <t>22H0536</t>
+  </si>
+  <si>
+    <t>22H0537</t>
+  </si>
+  <si>
+    <t>22H0538</t>
+  </si>
+  <si>
+    <t>22H0541</t>
+  </si>
+  <si>
+    <t>22H0542</t>
+  </si>
+  <si>
+    <t>22H0543</t>
+  </si>
+  <si>
+    <t>22H0621</t>
+  </si>
+  <si>
+    <t>22H06</t>
+  </si>
+  <si>
+    <t>22H0622</t>
+  </si>
+  <si>
+    <t>22H0623</t>
+  </si>
+  <si>
+    <t>22H0624</t>
+  </si>
+  <si>
+    <t>22H0625</t>
+  </si>
+  <si>
+    <t>22H0626</t>
+  </si>
+  <si>
+    <t>22H0627</t>
+  </si>
+  <si>
+    <t>22H0628</t>
+  </si>
+  <si>
+    <t>22H0629</t>
+  </si>
+  <si>
+    <t>22H06210</t>
+  </si>
+  <si>
+    <t>22H06211</t>
+  </si>
+  <si>
+    <t>22H06212</t>
+  </si>
+  <si>
+    <t>22H06213</t>
+  </si>
+  <si>
+    <t>22H0631</t>
+  </si>
+  <si>
+    <t>22H0632</t>
+  </si>
+  <si>
+    <t>22H0633</t>
+  </si>
+  <si>
+    <t>22H0634</t>
+  </si>
+  <si>
+    <t>22H0635</t>
+  </si>
+  <si>
+    <t>22H0636</t>
+  </si>
+  <si>
+    <t>22H0637</t>
+  </si>
+  <si>
+    <t>22H0638</t>
+  </si>
+  <si>
+    <t>22H0639</t>
+  </si>
+  <si>
+    <t>22H06310</t>
+  </si>
+  <si>
+    <t>22H06311</t>
+  </si>
+  <si>
+    <t>22H06312</t>
+  </si>
+  <si>
+    <t>22H06313</t>
+  </si>
+  <si>
+    <t>22H06314</t>
+  </si>
+  <si>
+    <t>22H06315</t>
+  </si>
+  <si>
+    <t>22H06316</t>
+  </si>
+  <si>
+    <t>22H06317</t>
+  </si>
+  <si>
+    <t>22H06318</t>
+  </si>
+  <si>
+    <t>22H06319</t>
+  </si>
+  <si>
+    <t>22H06320</t>
+  </si>
+  <si>
+    <t>22H06321</t>
+  </si>
+  <si>
+    <t>22H06322</t>
+  </si>
+  <si>
+    <t>22H06323</t>
+  </si>
+  <si>
+    <t>22H06324</t>
+  </si>
+  <si>
+    <t>22H06325</t>
+  </si>
+  <si>
+    <t>22H06326</t>
+  </si>
+  <si>
+    <t>22H06327</t>
+  </si>
+  <si>
+    <t>22H0641</t>
+  </si>
+  <si>
+    <t>22H0642</t>
+  </si>
+  <si>
+    <t>22H0643</t>
+  </si>
+  <si>
+    <t>22H0644</t>
+  </si>
+  <si>
+    <t>22H0645</t>
+  </si>
+  <si>
+    <t>22H0646</t>
+  </si>
+  <si>
+    <t>22H0647</t>
+  </si>
+  <si>
+    <t>22H0648</t>
+  </si>
+  <si>
+    <t>22H0649</t>
+  </si>
+  <si>
+    <t>22H06410</t>
+  </si>
+  <si>
+    <t>22H06411</t>
+  </si>
+  <si>
+    <t>22H06412</t>
+  </si>
+  <si>
+    <t>22H06413</t>
+  </si>
+  <si>
+    <t>22H06414</t>
+  </si>
+  <si>
+    <t>22H06415</t>
+  </si>
+  <si>
+    <t>22H06416</t>
+  </si>
+  <si>
+    <t>22H0821</t>
+  </si>
+  <si>
+    <t>22H08</t>
+  </si>
+  <si>
+    <t>22H0822</t>
+  </si>
+  <si>
+    <t>22H0831</t>
+  </si>
+  <si>
+    <t>22H0832</t>
+  </si>
+  <si>
+    <t>22H0833</t>
+  </si>
+  <si>
+    <t>22H0841</t>
+  </si>
+  <si>
+    <t>22H0921</t>
+  </si>
+  <si>
+    <t>22H09</t>
+  </si>
+  <si>
+    <t>22H0922</t>
+  </si>
+  <si>
+    <t>22H0923</t>
+  </si>
+  <si>
+    <t>22H0931</t>
+  </si>
+  <si>
+    <t>22H0932</t>
+  </si>
+  <si>
+    <t>22H0933</t>
+  </si>
+  <si>
+    <t>22H0934</t>
+  </si>
+  <si>
+    <t>22H0941</t>
+  </si>
+  <si>
+    <t>22H0942</t>
+  </si>
+  <si>
+    <t>수능수학</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수능영어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수능공사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수능공과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1418,10 +1449,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E10FC9C8-77A9-40E9-83AF-2D354710D832}">
-  <dimension ref="A1:G154"/>
+  <dimension ref="A1:H159"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1443,1083 +1474,1102 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="H1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="str">
+        <f>C2&amp;E2&amp;G2</f>
+        <v>22H0100</v>
+      </c>
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D3" t="s">
         <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" t="s">
         <v>13</v>
       </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>181</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>182</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>175</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8" t="s">
         <v>16</v>
       </c>
-      <c r="G4">
+      <c r="G8">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>183</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9" t="s">
         <v>17</v>
       </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10" t="s">
         <v>18</v>
       </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="G10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D11" t="s">
         <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-      <c r="F7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
-      </c>
-      <c r="F8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9">
-        <v>3</v>
-      </c>
-      <c r="F9" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10">
-        <v>4</v>
-      </c>
-      <c r="F10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" t="s">
-        <v>29</v>
       </c>
       <c r="E11">
         <v>4</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>186</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>175</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E12">
         <v>4</v>
       </c>
       <c r="F12" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>187</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>175</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>39</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="str">
+        <f>C14&amp;E14&amp;G14</f>
+        <v>22H0200</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>189</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>172</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>40</v>
+        <v>337</v>
       </c>
       <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>189</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="G15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>189</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="G16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>191</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>189</v>
+      </c>
+      <c r="D17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>192</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" t="s">
+        <v>189</v>
+      </c>
+      <c r="D18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18">
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17">
-        <v>2</v>
-      </c>
-      <c r="F17" t="s">
-        <v>46</v>
-      </c>
-      <c r="G17">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>193</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
+        <v>189</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18">
-        <v>2</v>
-      </c>
-      <c r="F18" t="s">
-        <v>48</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19">
-        <v>2</v>
-      </c>
-      <c r="F19" t="s">
-        <v>50</v>
-      </c>
-      <c r="G19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>194</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>189</v>
       </c>
       <c r="D20" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="G20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>195</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" t="s">
+        <v>189</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>196</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" t="s">
+        <v>189</v>
+      </c>
+      <c r="D22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22">
+        <v>3</v>
+      </c>
+      <c r="F22" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21">
-        <v>3</v>
-      </c>
-      <c r="F21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22">
-        <v>3</v>
-      </c>
-      <c r="F22" t="s">
-        <v>56</v>
-      </c>
-      <c r="G22">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>197</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>189</v>
       </c>
       <c r="D23" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="G23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>198</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" t="s">
+        <v>189</v>
+      </c>
+      <c r="D24" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>199</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" t="s">
+        <v>189</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25">
+        <v>3</v>
+      </c>
+      <c r="F25" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24">
-        <v>3</v>
-      </c>
-      <c r="F24" t="s">
-        <v>60</v>
-      </c>
-      <c r="G24">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>200</v>
+      </c>
+      <c r="B26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" t="s">
+        <v>189</v>
+      </c>
+      <c r="D26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26">
+        <v>3</v>
+      </c>
+      <c r="F26" t="s">
+        <v>35</v>
+      </c>
+      <c r="G26">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C25" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" t="s">
-        <v>29</v>
-      </c>
-      <c r="E25">
-        <v>4</v>
-      </c>
-      <c r="F25" t="s">
-        <v>62</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" t="s">
-        <v>37</v>
-      </c>
-      <c r="D26" t="s">
-        <v>29</v>
-      </c>
-      <c r="E26">
-        <v>4</v>
-      </c>
-      <c r="F26" t="s">
-        <v>64</v>
-      </c>
-      <c r="G26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>201</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>37</v>
+        <v>189</v>
       </c>
       <c r="D27" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E27">
         <v>4</v>
       </c>
       <c r="F27" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="G27">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>67</v>
+        <v>202</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>189</v>
       </c>
       <c r="D28" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E28">
+        <v>4</v>
+      </c>
+      <c r="F28" t="s">
+        <v>37</v>
+      </c>
+      <c r="G28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>203</v>
+      </c>
+      <c r="B29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" t="s">
+        <v>189</v>
+      </c>
+      <c r="D29" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29">
+        <v>4</v>
+      </c>
+      <c r="F29" t="s">
+        <v>38</v>
+      </c>
+      <c r="G29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" t="str">
+        <f>C30&amp;E30&amp;G30</f>
+        <v>22H0300</v>
+      </c>
+      <c r="B30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" t="s">
+        <v>205</v>
+      </c>
+      <c r="D30" t="s">
+        <v>172</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30" t="s">
+        <v>338</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>204</v>
+      </c>
+      <c r="B31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" t="s">
+        <v>205</v>
+      </c>
+      <c r="D31" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31">
         <v>1</v>
       </c>
-      <c r="F28" t="s">
-        <v>70</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>71</v>
-      </c>
-      <c r="B29" t="s">
-        <v>68</v>
-      </c>
-      <c r="C29" t="s">
-        <v>69</v>
-      </c>
-      <c r="D29" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="F29" t="s">
-        <v>72</v>
-      </c>
-      <c r="G29">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>73</v>
-      </c>
-      <c r="B30" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" t="s">
-        <v>69</v>
-      </c>
-      <c r="D30" t="s">
-        <v>10</v>
-      </c>
-      <c r="E30">
-        <v>1</v>
-      </c>
-      <c r="F30" t="s">
-        <v>74</v>
-      </c>
-      <c r="G30">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>75</v>
-      </c>
-      <c r="B31" t="s">
-        <v>68</v>
-      </c>
-      <c r="C31" t="s">
-        <v>69</v>
-      </c>
-      <c r="D31" t="s">
-        <v>15</v>
-      </c>
-      <c r="E31">
-        <v>2</v>
-      </c>
       <c r="F31" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>77</v>
+        <v>206</v>
       </c>
       <c r="B32" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="C32" t="s">
-        <v>69</v>
+        <v>205</v>
       </c>
       <c r="D32" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="G32">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>79</v>
+        <v>207</v>
       </c>
       <c r="B33" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="C33" t="s">
-        <v>69</v>
+        <v>205</v>
       </c>
       <c r="D33" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="G33">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>81</v>
+        <v>208</v>
       </c>
       <c r="B34" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="C34" t="s">
-        <v>69</v>
+        <v>205</v>
       </c>
       <c r="D34" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="G34">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>83</v>
+        <v>209</v>
       </c>
       <c r="B35" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>69</v>
+        <v>205</v>
       </c>
       <c r="D35" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="G35">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>85</v>
+        <v>210</v>
       </c>
       <c r="B36" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="C36" t="s">
-        <v>69</v>
+        <v>205</v>
       </c>
       <c r="D36" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F36" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="G36">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>87</v>
+        <v>211</v>
       </c>
       <c r="B37" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="C37" t="s">
-        <v>69</v>
+        <v>205</v>
       </c>
       <c r="D37" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E37">
         <v>3</v>
       </c>
       <c r="F37" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>212</v>
+      </c>
+      <c r="B38" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" t="s">
+        <v>205</v>
+      </c>
+      <c r="D38" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38">
+        <v>3</v>
+      </c>
+      <c r="F38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>213</v>
+      </c>
+      <c r="B39" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" t="s">
+        <v>205</v>
+      </c>
+      <c r="D39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39">
+        <v>3</v>
+      </c>
+      <c r="F39" t="s">
+        <v>48</v>
+      </c>
+      <c r="G39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>214</v>
+      </c>
+      <c r="B40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" t="s">
+        <v>205</v>
+      </c>
+      <c r="D40" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40">
+        <v>3</v>
+      </c>
+      <c r="F40" t="s">
+        <v>49</v>
+      </c>
+      <c r="G40">
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>89</v>
-      </c>
-      <c r="B38" t="s">
-        <v>68</v>
-      </c>
-      <c r="C38" t="s">
-        <v>69</v>
-      </c>
-      <c r="D38" t="s">
-        <v>22</v>
-      </c>
-      <c r="E38">
-        <v>3</v>
-      </c>
-      <c r="F38" t="s">
-        <v>90</v>
-      </c>
-      <c r="G38">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>215</v>
+      </c>
+      <c r="B41" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" t="s">
+        <v>205</v>
+      </c>
+      <c r="D41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41">
+        <v>3</v>
+      </c>
+      <c r="F41" t="s">
+        <v>50</v>
+      </c>
+      <c r="G41">
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>91</v>
-      </c>
-      <c r="B39" t="s">
-        <v>68</v>
-      </c>
-      <c r="C39" t="s">
-        <v>69</v>
-      </c>
-      <c r="D39" t="s">
-        <v>29</v>
-      </c>
-      <c r="E39">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>216</v>
+      </c>
+      <c r="B42" t="s">
+        <v>39</v>
+      </c>
+      <c r="C42" t="s">
+        <v>205</v>
+      </c>
+      <c r="D42" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42">
         <v>4</v>
       </c>
-      <c r="F39" t="s">
-        <v>92</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>93</v>
-      </c>
-      <c r="B40" t="s">
-        <v>68</v>
-      </c>
-      <c r="C40" t="s">
-        <v>69</v>
-      </c>
-      <c r="D40" t="s">
-        <v>29</v>
-      </c>
-      <c r="E40">
-        <v>4</v>
-      </c>
-      <c r="F40" t="s">
-        <v>94</v>
-      </c>
-      <c r="G40">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>95</v>
-      </c>
-      <c r="B41" t="s">
-        <v>68</v>
-      </c>
-      <c r="C41" t="s">
-        <v>69</v>
-      </c>
-      <c r="D41" t="s">
-        <v>29</v>
-      </c>
-      <c r="E41">
-        <v>4</v>
-      </c>
-      <c r="F41" t="s">
-        <v>96</v>
-      </c>
-      <c r="G41">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>97</v>
-      </c>
-      <c r="B42" t="s">
-        <v>98</v>
-      </c>
-      <c r="C42" t="s">
-        <v>99</v>
-      </c>
-      <c r="D42" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42">
-        <v>1</v>
-      </c>
       <c r="F42" t="s">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="G42">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>101</v>
+        <v>217</v>
       </c>
       <c r="B43" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="C43" t="s">
-        <v>99</v>
+        <v>205</v>
       </c>
       <c r="D43" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E43">
+        <v>4</v>
+      </c>
+      <c r="F43" t="s">
+        <v>52</v>
+      </c>
+      <c r="G43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>218</v>
+      </c>
+      <c r="B44" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" t="s">
+        <v>205</v>
+      </c>
+      <c r="D44" t="s">
+        <v>19</v>
+      </c>
+      <c r="E44">
+        <v>4</v>
+      </c>
+      <c r="F44" t="s">
+        <v>53</v>
+      </c>
+      <c r="G44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" t="str">
+        <f>C45&amp;E45&amp;G45</f>
+        <v>22H0400</v>
+      </c>
+      <c r="B45" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" t="s">
+        <v>220</v>
+      </c>
+      <c r="D45" t="s">
+        <v>172</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45" t="s">
+        <v>339</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>219</v>
+      </c>
+      <c r="B46" t="s">
+        <v>54</v>
+      </c>
+      <c r="C46" t="s">
+        <v>220</v>
+      </c>
+      <c r="D46" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46">
         <v>1</v>
       </c>
-      <c r="F43" t="s">
-        <v>102</v>
-      </c>
-      <c r="G43">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>103</v>
-      </c>
-      <c r="B44" t="s">
-        <v>98</v>
-      </c>
-      <c r="C44" t="s">
-        <v>99</v>
-      </c>
-      <c r="D44" t="s">
-        <v>10</v>
-      </c>
-      <c r="E44">
-        <v>1</v>
-      </c>
-      <c r="F44" t="s">
-        <v>104</v>
-      </c>
-      <c r="G44">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>105</v>
-      </c>
-      <c r="B45" t="s">
-        <v>98</v>
-      </c>
-      <c r="C45" t="s">
-        <v>99</v>
-      </c>
-      <c r="D45" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45">
-        <v>1</v>
-      </c>
-      <c r="F45" t="s">
-        <v>106</v>
-      </c>
-      <c r="G45">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>107</v>
-      </c>
-      <c r="B46" t="s">
-        <v>98</v>
-      </c>
-      <c r="C46" t="s">
-        <v>99</v>
-      </c>
-      <c r="D46" t="s">
-        <v>15</v>
-      </c>
-      <c r="E46">
-        <v>2</v>
-      </c>
       <c r="F46" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="G46">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>109</v>
+        <v>221</v>
       </c>
       <c r="B47" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C47" t="s">
-        <v>99</v>
+        <v>220</v>
       </c>
       <c r="D47" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="G47">
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>111</v>
+        <v>222</v>
       </c>
       <c r="B48" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C48" t="s">
-        <v>99</v>
+        <v>220</v>
       </c>
       <c r="D48" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="G48">
         <v>3</v>
@@ -2527,22 +2577,22 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>113</v>
+        <v>223</v>
       </c>
       <c r="B49" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C49" t="s">
-        <v>99</v>
+        <v>220</v>
       </c>
       <c r="D49" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="G49">
         <v>4</v>
@@ -2550,22 +2600,22 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>115</v>
+        <v>224</v>
       </c>
       <c r="B50" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>99</v>
+        <v>220</v>
       </c>
       <c r="D50" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F50" t="s">
-        <v>116</v>
+        <v>59</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -2573,22 +2623,22 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>117</v>
+        <v>225</v>
       </c>
       <c r="B51" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C51" t="s">
-        <v>99</v>
+        <v>220</v>
       </c>
       <c r="D51" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F51" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="G51">
         <v>2</v>
@@ -2596,22 +2646,22 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>119</v>
+        <v>226</v>
       </c>
       <c r="B52" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C52" t="s">
-        <v>99</v>
+        <v>220</v>
       </c>
       <c r="D52" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F52" t="s">
-        <v>120</v>
+        <v>61</v>
       </c>
       <c r="G52">
         <v>3</v>
@@ -2619,22 +2669,22 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>121</v>
+        <v>227</v>
       </c>
       <c r="B53" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C53" t="s">
-        <v>99</v>
+        <v>220</v>
       </c>
       <c r="D53" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F53" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="G53">
         <v>4</v>
@@ -2642,2115 +2692,2119 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>123</v>
+        <v>228</v>
       </c>
       <c r="B54" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C54" t="s">
-        <v>99</v>
+        <v>220</v>
       </c>
       <c r="D54" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E54">
         <v>3</v>
       </c>
       <c r="F54" t="s">
-        <v>124</v>
+        <v>63</v>
       </c>
       <c r="G54">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>125</v>
+        <v>229</v>
       </c>
       <c r="B55" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C55" t="s">
-        <v>99</v>
+        <v>220</v>
       </c>
       <c r="D55" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E55">
         <v>3</v>
       </c>
       <c r="F55" t="s">
-        <v>126</v>
+        <v>64</v>
       </c>
       <c r="G55">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>127</v>
+        <v>230</v>
       </c>
       <c r="B56" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>99</v>
+        <v>220</v>
       </c>
       <c r="D56" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E56">
         <v>3</v>
       </c>
       <c r="F56" t="s">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="G56">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>129</v>
+        <v>231</v>
       </c>
       <c r="B57" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C57" t="s">
-        <v>99</v>
+        <v>220</v>
       </c>
       <c r="D57" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E57">
         <v>3</v>
       </c>
       <c r="F57" t="s">
-        <v>130</v>
+        <v>66</v>
       </c>
       <c r="G57">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>131</v>
+        <v>232</v>
       </c>
       <c r="B58" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C58" t="s">
-        <v>99</v>
+        <v>220</v>
       </c>
       <c r="D58" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E58">
         <v>3</v>
       </c>
       <c r="F58" t="s">
-        <v>132</v>
+        <v>67</v>
       </c>
       <c r="G58">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>133</v>
+        <v>233</v>
       </c>
       <c r="B59" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C59" t="s">
-        <v>99</v>
+        <v>220</v>
       </c>
       <c r="D59" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F59" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>135</v>
+        <v>234</v>
       </c>
       <c r="B60" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C60" t="s">
-        <v>99</v>
+        <v>220</v>
       </c>
       <c r="D60" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F60" t="s">
-        <v>136</v>
+        <v>69</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>137</v>
+        <v>235</v>
       </c>
       <c r="B61" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C61" t="s">
-        <v>99</v>
+        <v>220</v>
       </c>
       <c r="D61" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>138</v>
+        <v>70</v>
       </c>
       <c r="G61">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>139</v>
+        <v>236</v>
       </c>
       <c r="B62" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C62" t="s">
-        <v>99</v>
+        <v>220</v>
       </c>
       <c r="D62" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F62" t="s">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="G62">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>141</v>
+        <v>237</v>
       </c>
       <c r="B63" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C63" t="s">
-        <v>99</v>
+        <v>220</v>
       </c>
       <c r="D63" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E63">
         <v>4</v>
       </c>
       <c r="F63" t="s">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="G63">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>143</v>
+        <v>238</v>
       </c>
       <c r="B64" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C64" t="s">
-        <v>99</v>
+        <v>220</v>
       </c>
       <c r="D64" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E64">
         <v>4</v>
       </c>
       <c r="F64" t="s">
-        <v>144</v>
+        <v>73</v>
       </c>
       <c r="G64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>239</v>
+      </c>
+      <c r="B65" t="s">
+        <v>54</v>
+      </c>
+      <c r="C65" t="s">
+        <v>220</v>
+      </c>
+      <c r="D65" t="s">
+        <v>19</v>
+      </c>
+      <c r="E65">
+        <v>4</v>
+      </c>
+      <c r="F65" t="s">
+        <v>74</v>
+      </c>
+      <c r="G65">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>240</v>
+      </c>
+      <c r="B66" t="s">
+        <v>54</v>
+      </c>
+      <c r="C66" t="s">
+        <v>220</v>
+      </c>
+      <c r="D66" t="s">
+        <v>19</v>
+      </c>
+      <c r="E66">
+        <v>4</v>
+      </c>
+      <c r="F66" t="s">
+        <v>75</v>
+      </c>
+      <c r="G66">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>241</v>
+      </c>
+      <c r="B67" t="s">
+        <v>54</v>
+      </c>
+      <c r="C67" t="s">
+        <v>220</v>
+      </c>
+      <c r="D67" t="s">
+        <v>19</v>
+      </c>
+      <c r="E67">
+        <v>4</v>
+      </c>
+      <c r="F67" t="s">
+        <v>76</v>
+      </c>
+      <c r="G67">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>242</v>
+      </c>
+      <c r="B68" t="s">
+        <v>54</v>
+      </c>
+      <c r="C68" t="s">
+        <v>220</v>
+      </c>
+      <c r="D68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E68">
+        <v>4</v>
+      </c>
+      <c r="F68" t="s">
+        <v>77</v>
+      </c>
+      <c r="G68">
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>145</v>
-      </c>
-      <c r="B65" t="s">
-        <v>146</v>
-      </c>
-      <c r="C65" t="s">
-        <v>147</v>
-      </c>
-      <c r="D65" t="s">
-        <v>10</v>
-      </c>
-      <c r="E65">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" t="str">
+        <f>C69&amp;E69&amp;G69</f>
+        <v>22H0500</v>
+      </c>
+      <c r="B69" t="s">
+        <v>78</v>
+      </c>
+      <c r="C69" t="s">
+        <v>244</v>
+      </c>
+      <c r="D69" t="s">
+        <v>172</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69" t="s">
+        <v>340</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>243</v>
+      </c>
+      <c r="B70" t="s">
+        <v>78</v>
+      </c>
+      <c r="C70" t="s">
+        <v>244</v>
+      </c>
+      <c r="D70" t="s">
+        <v>8</v>
+      </c>
+      <c r="E70">
         <v>1</v>
       </c>
-      <c r="F65" t="s">
-        <v>148</v>
-      </c>
-      <c r="G65">
+      <c r="F70" t="s">
+        <v>79</v>
+      </c>
+      <c r="G70">
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>149</v>
-      </c>
-      <c r="B66" t="s">
-        <v>146</v>
-      </c>
-      <c r="C66" t="s">
-        <v>147</v>
-      </c>
-      <c r="D66" t="s">
-        <v>10</v>
-      </c>
-      <c r="E66">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>245</v>
+      </c>
+      <c r="B71" t="s">
+        <v>78</v>
+      </c>
+      <c r="C71" t="s">
+        <v>244</v>
+      </c>
+      <c r="D71" t="s">
+        <v>8</v>
+      </c>
+      <c r="E71">
         <v>1</v>
       </c>
-      <c r="F66" t="s">
-        <v>150</v>
-      </c>
-      <c r="G66">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>151</v>
-      </c>
-      <c r="B67" t="s">
-        <v>146</v>
-      </c>
-      <c r="C67" t="s">
-        <v>147</v>
-      </c>
-      <c r="D67" t="s">
-        <v>10</v>
-      </c>
-      <c r="E67">
+      <c r="F71" t="s">
+        <v>80</v>
+      </c>
+      <c r="G71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>246</v>
+      </c>
+      <c r="B72" t="s">
+        <v>78</v>
+      </c>
+      <c r="C72" t="s">
+        <v>244</v>
+      </c>
+      <c r="D72" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72">
         <v>1</v>
       </c>
-      <c r="F67" t="s">
-        <v>152</v>
-      </c>
-      <c r="G67">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>153</v>
-      </c>
-      <c r="B68" t="s">
-        <v>146</v>
-      </c>
-      <c r="C68" t="s">
-        <v>147</v>
-      </c>
-      <c r="D68" t="s">
-        <v>10</v>
-      </c>
-      <c r="E68">
+      <c r="F72" t="s">
+        <v>81</v>
+      </c>
+      <c r="G72">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>247</v>
+      </c>
+      <c r="B73" t="s">
+        <v>78</v>
+      </c>
+      <c r="C73" t="s">
+        <v>244</v>
+      </c>
+      <c r="D73" t="s">
+        <v>8</v>
+      </c>
+      <c r="E73">
         <v>1</v>
       </c>
-      <c r="F68" t="s">
-        <v>154</v>
-      </c>
-      <c r="G68">
+      <c r="F73" t="s">
+        <v>82</v>
+      </c>
+      <c r="G73">
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>155</v>
-      </c>
-      <c r="B69" t="s">
-        <v>146</v>
-      </c>
-      <c r="C69" t="s">
-        <v>147</v>
-      </c>
-      <c r="D69" t="s">
-        <v>15</v>
-      </c>
-      <c r="E69">
-        <v>2</v>
-      </c>
-      <c r="F69" t="s">
-        <v>156</v>
-      </c>
-      <c r="G69">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>248</v>
+      </c>
+      <c r="B74" t="s">
+        <v>78</v>
+      </c>
+      <c r="C74" t="s">
+        <v>244</v>
+      </c>
+      <c r="D74" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74">
+        <v>2</v>
+      </c>
+      <c r="F74" t="s">
+        <v>83</v>
+      </c>
+      <c r="G74">
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>157</v>
-      </c>
-      <c r="B70" t="s">
-        <v>146</v>
-      </c>
-      <c r="C70" t="s">
-        <v>147</v>
-      </c>
-      <c r="D70" t="s">
-        <v>15</v>
-      </c>
-      <c r="E70">
-        <v>2</v>
-      </c>
-      <c r="F70" t="s">
-        <v>158</v>
-      </c>
-      <c r="G70">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>159</v>
-      </c>
-      <c r="B71" t="s">
-        <v>146</v>
-      </c>
-      <c r="C71" t="s">
-        <v>147</v>
-      </c>
-      <c r="D71" t="s">
-        <v>15</v>
-      </c>
-      <c r="E71">
-        <v>2</v>
-      </c>
-      <c r="F71" t="s">
-        <v>160</v>
-      </c>
-      <c r="G71">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>161</v>
-      </c>
-      <c r="B72" t="s">
-        <v>146</v>
-      </c>
-      <c r="C72" t="s">
-        <v>147</v>
-      </c>
-      <c r="D72" t="s">
-        <v>15</v>
-      </c>
-      <c r="E72">
-        <v>2</v>
-      </c>
-      <c r="F72" t="s">
-        <v>162</v>
-      </c>
-      <c r="G72">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>249</v>
+      </c>
+      <c r="B75" t="s">
+        <v>78</v>
+      </c>
+      <c r="C75" t="s">
+        <v>244</v>
+      </c>
+      <c r="D75" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75">
+        <v>2</v>
+      </c>
+      <c r="F75" t="s">
+        <v>84</v>
+      </c>
+      <c r="G75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>250</v>
+      </c>
+      <c r="B76" t="s">
+        <v>78</v>
+      </c>
+      <c r="C76" t="s">
+        <v>244</v>
+      </c>
+      <c r="D76" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76">
+        <v>2</v>
+      </c>
+      <c r="F76" t="s">
+        <v>85</v>
+      </c>
+      <c r="G76">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>251</v>
+      </c>
+      <c r="B77" t="s">
+        <v>78</v>
+      </c>
+      <c r="C77" t="s">
+        <v>244</v>
+      </c>
+      <c r="D77" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77">
+        <v>2</v>
+      </c>
+      <c r="F77" t="s">
+        <v>86</v>
+      </c>
+      <c r="G77">
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>163</v>
-      </c>
-      <c r="B73" t="s">
-        <v>146</v>
-      </c>
-      <c r="C73" t="s">
-        <v>147</v>
-      </c>
-      <c r="D73" t="s">
-        <v>22</v>
-      </c>
-      <c r="E73">
-        <v>3</v>
-      </c>
-      <c r="F73" t="s">
-        <v>164</v>
-      </c>
-      <c r="G73">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>252</v>
+      </c>
+      <c r="B78" t="s">
+        <v>78</v>
+      </c>
+      <c r="C78" t="s">
+        <v>244</v>
+      </c>
+      <c r="D78" t="s">
+        <v>15</v>
+      </c>
+      <c r="E78">
+        <v>3</v>
+      </c>
+      <c r="F78" t="s">
+        <v>87</v>
+      </c>
+      <c r="G78">
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>165</v>
-      </c>
-      <c r="B74" t="s">
-        <v>146</v>
-      </c>
-      <c r="C74" t="s">
-        <v>147</v>
-      </c>
-      <c r="D74" t="s">
-        <v>22</v>
-      </c>
-      <c r="E74">
-        <v>3</v>
-      </c>
-      <c r="F74" t="s">
-        <v>166</v>
-      </c>
-      <c r="G74">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>167</v>
-      </c>
-      <c r="B75" t="s">
-        <v>146</v>
-      </c>
-      <c r="C75" t="s">
-        <v>147</v>
-      </c>
-      <c r="D75" t="s">
-        <v>22</v>
-      </c>
-      <c r="E75">
-        <v>3</v>
-      </c>
-      <c r="F75" t="s">
-        <v>168</v>
-      </c>
-      <c r="G75">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>169</v>
-      </c>
-      <c r="B76" t="s">
-        <v>146</v>
-      </c>
-      <c r="C76" t="s">
-        <v>147</v>
-      </c>
-      <c r="D76" t="s">
-        <v>22</v>
-      </c>
-      <c r="E76">
-        <v>3</v>
-      </c>
-      <c r="F76" t="s">
-        <v>170</v>
-      </c>
-      <c r="G76">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>171</v>
-      </c>
-      <c r="B77" t="s">
-        <v>146</v>
-      </c>
-      <c r="C77" t="s">
-        <v>147</v>
-      </c>
-      <c r="D77" t="s">
-        <v>22</v>
-      </c>
-      <c r="E77">
-        <v>3</v>
-      </c>
-      <c r="F77" t="s">
-        <v>172</v>
-      </c>
-      <c r="G77">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>173</v>
-      </c>
-      <c r="B78" t="s">
-        <v>146</v>
-      </c>
-      <c r="C78" t="s">
-        <v>147</v>
-      </c>
-      <c r="D78" t="s">
-        <v>22</v>
-      </c>
-      <c r="E78">
-        <v>3</v>
-      </c>
-      <c r="F78" t="s">
-        <v>174</v>
-      </c>
-      <c r="G78">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>175</v>
+        <v>253</v>
       </c>
       <c r="B79" t="s">
-        <v>146</v>
+        <v>78</v>
       </c>
       <c r="C79" t="s">
-        <v>147</v>
+        <v>244</v>
       </c>
       <c r="D79" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E79">
         <v>3</v>
       </c>
       <c r="F79" t="s">
-        <v>176</v>
+        <v>88</v>
       </c>
       <c r="G79">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="B80" t="s">
-        <v>146</v>
+        <v>78</v>
       </c>
       <c r="C80" t="s">
-        <v>147</v>
+        <v>244</v>
       </c>
       <c r="D80" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E80">
         <v>3</v>
       </c>
       <c r="F80" t="s">
-        <v>178</v>
+        <v>89</v>
       </c>
       <c r="G80">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>179</v>
+        <v>255</v>
       </c>
       <c r="B81" t="s">
-        <v>146</v>
+        <v>78</v>
       </c>
       <c r="C81" t="s">
-        <v>147</v>
+        <v>244</v>
       </c>
       <c r="D81" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E81">
+        <v>3</v>
+      </c>
+      <c r="F81" t="s">
+        <v>90</v>
+      </c>
+      <c r="G81">
         <v>4</v>
-      </c>
-      <c r="F81" t="s">
-        <v>180</v>
-      </c>
-      <c r="G81">
-        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="B82" t="s">
-        <v>146</v>
+        <v>78</v>
       </c>
       <c r="C82" t="s">
-        <v>147</v>
+        <v>244</v>
       </c>
       <c r="D82" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E82">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F82" t="s">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="G82">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>183</v>
+        <v>257</v>
       </c>
       <c r="B83" t="s">
-        <v>146</v>
+        <v>78</v>
       </c>
       <c r="C83" t="s">
-        <v>147</v>
+        <v>244</v>
       </c>
       <c r="D83" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E83">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F83" t="s">
-        <v>184</v>
+        <v>92</v>
       </c>
       <c r="G83">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>185</v>
+        <v>258</v>
       </c>
       <c r="B84" t="s">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="C84" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="D84" t="s">
         <v>15</v>
       </c>
       <c r="E84">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F84" t="s">
-        <v>188</v>
+        <v>93</v>
       </c>
       <c r="G84">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>189</v>
+        <v>259</v>
       </c>
       <c r="B85" t="s">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="C85" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="D85" t="s">
         <v>15</v>
       </c>
       <c r="E85">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F85" t="s">
-        <v>190</v>
+        <v>94</v>
       </c>
       <c r="G85">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>191</v>
+        <v>260</v>
       </c>
       <c r="B86" t="s">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="C86" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="D86" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E86">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F86" t="s">
-        <v>192</v>
+        <v>95</v>
       </c>
       <c r="G86">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>193</v>
+        <v>261</v>
       </c>
       <c r="B87" t="s">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="C87" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="D87" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E87">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F87" t="s">
-        <v>194</v>
+        <v>96</v>
       </c>
       <c r="G87">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>195</v>
+        <v>262</v>
       </c>
       <c r="B88" t="s">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="C88" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="D88" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E88">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F88" t="s">
-        <v>196</v>
+        <v>97</v>
       </c>
       <c r="G88">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>197</v>
+        <v>263</v>
       </c>
       <c r="B89" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C89" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E89">
         <v>2</v>
       </c>
       <c r="F89" t="s">
-        <v>198</v>
+        <v>99</v>
       </c>
       <c r="G89">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>199</v>
+        <v>265</v>
       </c>
       <c r="B90" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C90" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E90">
         <v>2</v>
       </c>
       <c r="F90" t="s">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G90">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>201</v>
+        <v>266</v>
       </c>
       <c r="B91" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C91" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E91">
         <v>2</v>
       </c>
       <c r="F91" t="s">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="G91">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>203</v>
+        <v>267</v>
       </c>
       <c r="B92" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C92" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E92">
         <v>2</v>
       </c>
       <c r="F92" t="s">
-        <v>204</v>
+        <v>102</v>
       </c>
       <c r="G92">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>205</v>
+        <v>268</v>
       </c>
       <c r="B93" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C93" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E93">
         <v>2</v>
       </c>
       <c r="F93" t="s">
-        <v>206</v>
+        <v>103</v>
       </c>
       <c r="G93">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>207</v>
+        <v>269</v>
       </c>
       <c r="B94" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C94" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E94">
         <v>2</v>
       </c>
       <c r="F94" t="s">
-        <v>208</v>
+        <v>104</v>
       </c>
       <c r="G94">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>209</v>
+        <v>270</v>
       </c>
       <c r="B95" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C95" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E95">
         <v>2</v>
       </c>
       <c r="F95" t="s">
-        <v>210</v>
+        <v>105</v>
       </c>
       <c r="G95">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>211</v>
+        <v>271</v>
       </c>
       <c r="B96" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C96" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E96">
         <v>2</v>
       </c>
       <c r="F96" t="s">
-        <v>212</v>
+        <v>106</v>
       </c>
       <c r="G96">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>213</v>
+        <v>272</v>
       </c>
       <c r="B97" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C97" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E97">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F97" t="s">
-        <v>214</v>
+        <v>107</v>
       </c>
       <c r="G97">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>215</v>
+        <v>273</v>
       </c>
       <c r="B98" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C98" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E98">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F98" t="s">
-        <v>216</v>
+        <v>108</v>
       </c>
       <c r="G98">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>217</v>
+        <v>274</v>
       </c>
       <c r="B99" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C99" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E99">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F99" t="s">
-        <v>218</v>
+        <v>109</v>
       </c>
       <c r="G99">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>219</v>
+        <v>275</v>
       </c>
       <c r="B100" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C100" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E100">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F100" t="s">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="G100">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>221</v>
+        <v>276</v>
       </c>
       <c r="B101" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C101" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E101">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F101" t="s">
-        <v>222</v>
+        <v>111</v>
       </c>
       <c r="G101">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>223</v>
+        <v>277</v>
       </c>
       <c r="B102" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C102" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E102">
         <v>3</v>
       </c>
       <c r="F102" t="s">
-        <v>224</v>
+        <v>112</v>
       </c>
       <c r="G102">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="B103" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C103" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E103">
         <v>3</v>
       </c>
       <c r="F103" t="s">
-        <v>226</v>
+        <v>113</v>
       </c>
       <c r="G103">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
       <c r="B104" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C104" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E104">
         <v>3</v>
       </c>
       <c r="F104" t="s">
-        <v>228</v>
+        <v>114</v>
       </c>
       <c r="G104">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>229</v>
+        <v>280</v>
       </c>
       <c r="B105" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C105" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D105" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E105">
         <v>3</v>
       </c>
       <c r="F105" t="s">
-        <v>230</v>
+        <v>115</v>
       </c>
       <c r="G105">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>231</v>
+        <v>281</v>
       </c>
       <c r="B106" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C106" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D106" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E106">
         <v>3</v>
       </c>
       <c r="F106" t="s">
-        <v>232</v>
+        <v>116</v>
       </c>
       <c r="G106">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>233</v>
+        <v>282</v>
       </c>
       <c r="B107" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C107" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E107">
         <v>3</v>
       </c>
       <c r="F107" t="s">
-        <v>234</v>
+        <v>117</v>
       </c>
       <c r="G107">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>235</v>
+        <v>283</v>
       </c>
       <c r="B108" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C108" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D108" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E108">
         <v>3</v>
       </c>
       <c r="F108" t="s">
-        <v>236</v>
+        <v>118</v>
       </c>
       <c r="G108">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>237</v>
+        <v>284</v>
       </c>
       <c r="B109" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C109" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D109" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E109">
         <v>3</v>
       </c>
       <c r="F109" t="s">
-        <v>238</v>
+        <v>119</v>
       </c>
       <c r="G109">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>239</v>
+        <v>285</v>
       </c>
       <c r="B110" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C110" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D110" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E110">
         <v>3</v>
       </c>
       <c r="F110" t="s">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="G110">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>241</v>
+        <v>286</v>
       </c>
       <c r="B111" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C111" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D111" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E111">
         <v>3</v>
       </c>
       <c r="F111" t="s">
-        <v>242</v>
+        <v>121</v>
       </c>
       <c r="G111">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>243</v>
+        <v>287</v>
       </c>
       <c r="B112" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C112" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D112" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E112">
         <v>3</v>
       </c>
       <c r="F112" t="s">
-        <v>244</v>
+        <v>122</v>
       </c>
       <c r="G112">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>245</v>
+        <v>288</v>
       </c>
       <c r="B113" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C113" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D113" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E113">
         <v>3</v>
       </c>
       <c r="F113" t="s">
-        <v>246</v>
+        <v>123</v>
       </c>
       <c r="G113">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>247</v>
+        <v>289</v>
       </c>
       <c r="B114" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C114" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D114" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E114">
         <v>3</v>
       </c>
       <c r="F114" t="s">
-        <v>248</v>
+        <v>124</v>
       </c>
       <c r="G114">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="B115" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C115" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E115">
         <v>3</v>
       </c>
       <c r="F115" t="s">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="G115">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>251</v>
+        <v>291</v>
       </c>
       <c r="B116" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C116" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E116">
         <v>3</v>
       </c>
       <c r="F116" t="s">
-        <v>252</v>
+        <v>126</v>
       </c>
       <c r="G116">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>253</v>
+        <v>292</v>
       </c>
       <c r="B117" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C117" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D117" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E117">
         <v>3</v>
       </c>
       <c r="F117" t="s">
-        <v>254</v>
+        <v>127</v>
       </c>
       <c r="G117">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>255</v>
+        <v>293</v>
       </c>
       <c r="B118" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C118" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E118">
         <v>3</v>
       </c>
       <c r="F118" t="s">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="G118">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>257</v>
+        <v>294</v>
       </c>
       <c r="B119" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C119" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E119">
         <v>3</v>
       </c>
       <c r="F119" t="s">
-        <v>258</v>
+        <v>129</v>
       </c>
       <c r="G119">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="B120" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C120" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E120">
         <v>3</v>
       </c>
       <c r="F120" t="s">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="G120">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>261</v>
+        <v>296</v>
       </c>
       <c r="B121" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C121" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D121" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E121">
         <v>3</v>
       </c>
       <c r="F121" t="s">
-        <v>262</v>
+        <v>131</v>
       </c>
       <c r="G121">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="B122" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C122" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D122" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E122">
         <v>3</v>
       </c>
       <c r="F122" t="s">
-        <v>264</v>
+        <v>132</v>
       </c>
       <c r="G122">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>265</v>
+        <v>298</v>
       </c>
       <c r="B123" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C123" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D123" t="s">
+        <v>15</v>
+      </c>
+      <c r="E123">
+        <v>3</v>
+      </c>
+      <c r="F123" t="s">
+        <v>133</v>
+      </c>
+      <c r="G123">
         <v>22</v>
-      </c>
-      <c r="E123">
-        <v>3</v>
-      </c>
-      <c r="F123" t="s">
-        <v>266</v>
-      </c>
-      <c r="G123">
-        <v>27</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="B124" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C124" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D124" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E124">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F124" t="s">
-        <v>268</v>
+        <v>134</v>
       </c>
       <c r="G124">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="B125" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C125" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D125" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E125">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F125" t="s">
-        <v>270</v>
+        <v>135</v>
       </c>
       <c r="G125">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B126" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C126" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D126" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E126">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F126" t="s">
-        <v>272</v>
+        <v>136</v>
       </c>
       <c r="G126">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>273</v>
+        <v>302</v>
       </c>
       <c r="B127" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C127" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D127" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E127">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F127" t="s">
-        <v>274</v>
+        <v>137</v>
       </c>
       <c r="G127">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>275</v>
+        <v>303</v>
       </c>
       <c r="B128" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C128" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E128">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F128" t="s">
-        <v>276</v>
+        <v>138</v>
       </c>
       <c r="G128">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="B129" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C129" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E129">
         <v>4</v>
       </c>
       <c r="F129" t="s">
-        <v>278</v>
+        <v>139</v>
       </c>
       <c r="G129">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="B130" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C130" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E130">
         <v>4</v>
       </c>
       <c r="F130" t="s">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="G130">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>281</v>
+        <v>306</v>
       </c>
       <c r="B131" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C131" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E131">
         <v>4</v>
       </c>
       <c r="F131" t="s">
-        <v>282</v>
+        <v>141</v>
       </c>
       <c r="G131">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="B132" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C132" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E132">
         <v>4</v>
       </c>
       <c r="F132" t="s">
-        <v>284</v>
+        <v>142</v>
       </c>
       <c r="G132">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="B133" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C133" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E133">
         <v>4</v>
       </c>
       <c r="F133" t="s">
-        <v>286</v>
+        <v>143</v>
       </c>
       <c r="G133">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="B134" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C134" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E134">
         <v>4</v>
       </c>
       <c r="F134" t="s">
-        <v>288</v>
+        <v>144</v>
       </c>
       <c r="G134">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="B135" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C135" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E135">
         <v>4</v>
       </c>
       <c r="F135" t="s">
-        <v>290</v>
+        <v>145</v>
       </c>
       <c r="G135">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="B136" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C136" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D136" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E136">
         <v>4</v>
       </c>
       <c r="F136" t="s">
-        <v>292</v>
+        <v>146</v>
       </c>
       <c r="G136">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="B137" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C137" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D137" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E137">
         <v>4</v>
       </c>
       <c r="F137" t="s">
-        <v>294</v>
+        <v>147</v>
       </c>
       <c r="G137">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="B138" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C138" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D138" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E138">
         <v>4</v>
       </c>
       <c r="F138" t="s">
-        <v>296</v>
+        <v>148</v>
       </c>
       <c r="G138">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="B139" t="s">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="C139" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="D139" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E139">
         <v>4</v>
       </c>
       <c r="F139" t="s">
-        <v>298</v>
+        <v>149</v>
       </c>
       <c r="G139">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="B140" t="s">
-        <v>300</v>
+        <v>98</v>
       </c>
       <c r="C140" t="s">
-        <v>301</v>
+        <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E140">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F140" t="s">
-        <v>302</v>
+        <v>150</v>
       </c>
       <c r="G140">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="B141" t="s">
-        <v>300</v>
+        <v>98</v>
       </c>
       <c r="C141" t="s">
-        <v>301</v>
+        <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E141">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F141" t="s">
-        <v>304</v>
+        <v>151</v>
       </c>
       <c r="G141">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="B142" t="s">
-        <v>300</v>
+        <v>98</v>
       </c>
       <c r="C142" t="s">
-        <v>301</v>
+        <v>264</v>
       </c>
       <c r="D142" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E142">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F142" t="s">
-        <v>306</v>
+        <v>152</v>
       </c>
       <c r="G142">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="B143" t="s">
-        <v>300</v>
+        <v>98</v>
       </c>
       <c r="C143" t="s">
-        <v>301</v>
+        <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E143">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F143" t="s">
-        <v>308</v>
+        <v>153</v>
       </c>
       <c r="G143">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="B144" t="s">
-        <v>300</v>
+        <v>98</v>
       </c>
       <c r="C144" t="s">
-        <v>301</v>
+        <v>264</v>
       </c>
       <c r="D144" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E144">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F144" t="s">
-        <v>310</v>
+        <v>154</v>
       </c>
       <c r="G144">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="B145" t="s">
-        <v>300</v>
+        <v>155</v>
       </c>
       <c r="C145" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="D145" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="E145">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F145" t="s">
-        <v>312</v>
+        <v>156</v>
       </c>
       <c r="G145">
         <v>1</v>
@@ -4758,186 +4812,186 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="B146" t="s">
-        <v>314</v>
+        <v>155</v>
       </c>
       <c r="C146" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D146" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E146">
         <v>2</v>
       </c>
       <c r="F146" t="s">
-        <v>316</v>
+        <v>157</v>
       </c>
       <c r="G146">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B147" t="s">
-        <v>314</v>
+        <v>155</v>
       </c>
       <c r="C147" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D147" t="s">
         <v>15</v>
       </c>
       <c r="E147">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F147" t="s">
-        <v>318</v>
+        <v>158</v>
       </c>
       <c r="G147">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B148" t="s">
-        <v>314</v>
+        <v>155</v>
       </c>
       <c r="C148" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D148" t="s">
         <v>15</v>
       </c>
       <c r="E148">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F148" t="s">
-        <v>320</v>
+        <v>159</v>
       </c>
       <c r="G148">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
+        <v>325</v>
+      </c>
+      <c r="B149" t="s">
+        <v>155</v>
+      </c>
+      <c r="C149" t="s">
         <v>321</v>
       </c>
-      <c r="B149" t="s">
-        <v>314</v>
-      </c>
-      <c r="C149" t="s">
-        <v>315</v>
-      </c>
       <c r="D149" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E149">
         <v>3</v>
       </c>
       <c r="F149" t="s">
-        <v>322</v>
+        <v>160</v>
       </c>
       <c r="G149">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B150" t="s">
-        <v>314</v>
+        <v>155</v>
       </c>
       <c r="C150" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D150" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E150">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F150" t="s">
-        <v>324</v>
+        <v>161</v>
       </c>
       <c r="G150">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B151" t="s">
-        <v>314</v>
+        <v>162</v>
       </c>
       <c r="C151" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="D151" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E151">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F151" t="s">
-        <v>326</v>
+        <v>163</v>
       </c>
       <c r="G151">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B152" t="s">
-        <v>314</v>
+        <v>162</v>
       </c>
       <c r="C152" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="D152" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E152">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F152" t="s">
-        <v>328</v>
+        <v>164</v>
       </c>
       <c r="G152">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B153" t="s">
-        <v>314</v>
+        <v>162</v>
       </c>
       <c r="C153" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="D153" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="E153">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F153" t="s">
-        <v>330</v>
+        <v>165</v>
       </c>
       <c r="G153">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
@@ -4945,21 +4999,136 @@
         <v>331</v>
       </c>
       <c r="B154" t="s">
-        <v>314</v>
+        <v>162</v>
       </c>
       <c r="C154" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="D154" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E154">
+        <v>3</v>
+      </c>
+      <c r="F154" t="s">
+        <v>166</v>
+      </c>
+      <c r="G154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>332</v>
+      </c>
+      <c r="B155" t="s">
+        <v>162</v>
+      </c>
+      <c r="C155" t="s">
+        <v>328</v>
+      </c>
+      <c r="D155" t="s">
+        <v>15</v>
+      </c>
+      <c r="E155">
+        <v>3</v>
+      </c>
+      <c r="F155" t="s">
+        <v>167</v>
+      </c>
+      <c r="G155">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>333</v>
+      </c>
+      <c r="B156" t="s">
+        <v>162</v>
+      </c>
+      <c r="C156" t="s">
+        <v>328</v>
+      </c>
+      <c r="D156" t="s">
+        <v>15</v>
+      </c>
+      <c r="E156">
+        <v>3</v>
+      </c>
+      <c r="F156" t="s">
+        <v>168</v>
+      </c>
+      <c r="G156">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>334</v>
+      </c>
+      <c r="B157" t="s">
+        <v>162</v>
+      </c>
+      <c r="C157" t="s">
+        <v>328</v>
+      </c>
+      <c r="D157" t="s">
+        <v>15</v>
+      </c>
+      <c r="E157">
+        <v>3</v>
+      </c>
+      <c r="F157" t="s">
+        <v>169</v>
+      </c>
+      <c r="G157">
         <v>4</v>
       </c>
-      <c r="F154" t="s">
-        <v>332</v>
-      </c>
-      <c r="G154">
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>335</v>
+      </c>
+      <c r="B158" t="s">
+        <v>162</v>
+      </c>
+      <c r="C158" t="s">
+        <v>328</v>
+      </c>
+      <c r="D158" t="s">
+        <v>19</v>
+      </c>
+      <c r="E158">
+        <v>4</v>
+      </c>
+      <c r="F158" t="s">
+        <v>170</v>
+      </c>
+      <c r="G158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>336</v>
+      </c>
+      <c r="B159" t="s">
+        <v>162</v>
+      </c>
+      <c r="C159" t="s">
+        <v>328</v>
+      </c>
+      <c r="D159" t="s">
+        <v>19</v>
+      </c>
+      <c r="E159">
+        <v>4</v>
+      </c>
+      <c r="F159" t="s">
+        <v>171</v>
+      </c>
+      <c r="G159">
         <v>2</v>
       </c>
     </row>
